--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -30,10 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -48,88 +48,80 @@
     <t>!string</t>
   </si>
   <si>
-    <t>Gold</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>Dia</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>GoldDungeonTicket</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ExpDungeonTicket</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RaidTicket</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>투기장 티켓</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>PVPTicket</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 티켓</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 티켓</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>레이드 티켓</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenAmount</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenMax</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>레이드 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경험치 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>투기장 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CurrencyInfo</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -157,7 +149,7 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -174,19 +166,19 @@
       </rPr>
       <t>bool</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenInterval</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Regenable</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>NavigationLink</t>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -203,7 +195,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -220,19 +212,43 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="6" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gold</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruby</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>강화석</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -361,55 +377,55 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -693,7 +709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -701,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="4" bestFit="1" customWidth="1"/>
@@ -717,10 +733,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -738,27 +754,27 @@
         <v>3</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F2" s="13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G2" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>28</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -767,19 +783,19 @@
         <v>4</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F3" s="13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>0</v>
@@ -787,10 +803,10 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -798,47 +814,33 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
-        <v>7</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>22</v>
-      </c>
+        <v>34</v>
+      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1"/>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1800</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
+      <c r="F6" s="1"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>21</v>
@@ -860,10 +862,10 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>20</v>
@@ -873,25 +875,25 @@
         <v>1</v>
       </c>
       <c r="G8">
-        <v>3600</v>
+        <v>1800</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="9" t="s">
-        <v>13</v>
+      <c r="B9" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="b">
@@ -900,25 +902,41 @@
       <c r="G9">
         <v>3600</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9">
         <v>1</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9">
         <v>5</v>
       </c>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
+      <c r="A10" s="8"/>
+      <c r="B10" s="9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>3600</v>
+      </c>
+      <c r="H10" s="1">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1">
+        <v>5</v>
+      </c>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A11" s="8"/>
       <c r="B11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -938,9 +956,11 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
@@ -998,8 +1018,15 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="8"/>
+      <c r="B22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+    </row>
   </sheetData>
-  <phoneticPr fontId="6" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -120,10 +120,6 @@
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
-    <t>CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>!</t>
     </r>
@@ -228,6 +224,10 @@
   </si>
   <si>
     <t>강화석</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyInfo</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
@@ -413,9 +413,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -426,6 +423,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -732,11 +732,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B1" s="11" t="s">
+      <c r="A1" s="11" t="s">
         <v>23</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>34</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -753,14 +753,14 @@
       <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="G2" s="14" t="s">
+      <c r="E2" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="F2" s="12" t="s">
         <v>26</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>25</v>
       </c>
       <c r="H2" s="10" t="s">
         <v>16</v>
@@ -768,13 +768,13 @@
       <c r="I2" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="J2" s="14" t="s">
-        <v>28</v>
+      <c r="J2" s="13" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -782,11 +782,11 @@
       <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>25</v>
+      <c r="E3" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="12" t="s">
+        <v>24</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>17</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>
@@ -825,10 +825,10 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C6" t="s">
         <v>33</v>
-      </c>
-      <c r="C6" t="s">
-        <v>34</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -30,10 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -49,75 +49,75 @@
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>GoldDungeonTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ExpDungeonTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RaidTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>투기장 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PVPTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>레이드 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenAmount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenMax</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>레이드 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>투기장 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -145,7 +145,7 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -162,19 +162,19 @@
       </rPr>
       <t>bool</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenInterval</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Regenable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NavigationLink</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -191,7 +191,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -208,39 +208,39 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>Ruby</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>강화석</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -377,55 +377,55 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -709,7 +709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -717,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="4" bestFit="1" customWidth="1"/>
@@ -736,7 +736,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -824,26 +824,40 @@
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
-        <v>32</v>
+        <v>6</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
-      </c>
-      <c r="D6" s="1"/>
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+      <c r="F6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1800</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="b">
@@ -862,38 +876,38 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C8" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="b">
         <v>1</v>
       </c>
       <c r="G8">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="H8">
         <v>1</v>
       </c>
       <c r="I8">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="1" t="s">
-        <v>8</v>
+      <c r="B9" s="9" t="s">
+        <v>12</v>
       </c>
       <c r="C9" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="b">
@@ -902,41 +916,25 @@
       <c r="G9">
         <v>3600</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="1">
         <v>1</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="1">
         <v>5</v>
       </c>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="9" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>3600</v>
-      </c>
-      <c r="H10" s="1">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1">
-        <v>5</v>
-      </c>
+      <c r="B10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
       <c r="J10" s="1"/>
       <c r="K10" s="1"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A11" s="8"/>
       <c r="B11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -956,11 +954,9 @@
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
@@ -1018,15 +1014,8 @@
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="8"/>
-      <c r="B22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -211,15 +211,15 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>Gold</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>CurrencyInfo</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Gold</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>CurrencyInfo</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -709,7 +709,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -736,7 +736,7 @@
         <v>23</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -774,7 +774,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -803,7 +803,7 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C4" t="s">
         <v>9</v>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>!int</t>
     <phoneticPr fontId="8" type="noConversion"/>
@@ -46,10 +46,6 @@
   </si>
   <si>
     <t>!string</t>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>GoldDungeonTicket</t>
@@ -221,6 +217,16 @@
   <si>
     <t>!CurrencyInfo</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Coin_Gold</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gem_Diamond_Blue</t>
   </si>
 </sst>
 </file>
@@ -724,7 +730,7 @@
     <col min="2" max="2" width="19.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.75" customWidth="1"/>
+    <col min="5" max="5" width="28.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="13.375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="14.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.125" customWidth="1"/>
@@ -733,10 +739,10 @@
   <sheetData>
     <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -754,27 +760,27 @@
         <v>3</v>
       </c>
       <c r="E2" s="14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F2" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="13" t="s">
         <v>26</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="H2" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="10" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -783,19 +789,19 @@
         <v>4</v>
       </c>
       <c r="E3" s="14" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G3" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H3" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="I3" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J3" s="10" t="s">
         <v>0</v>
@@ -803,36 +809,40 @@
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
+      <c r="E4" s="1" t="s">
+        <v>33</v>
+      </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
+      <c r="E5" s="1" t="s">
+        <v>34</v>
+      </c>
       <c r="F5" s="1"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="1" t="b">
@@ -851,13 +861,13 @@
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C7" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="1" t="b">
@@ -876,13 +886,13 @@
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="b">
@@ -901,13 +911,13 @@
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="b">

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -33,7 +33,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -49,71 +49,71 @@
   </si>
   <si>
     <t>GoldDungeonTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ExpDungeonTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RaidTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>투기장 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>PVPTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>레이드 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenAmount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenMax</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>레이드 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경험치 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>투기장 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -141,7 +141,7 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -158,19 +158,19 @@
       </rPr>
       <t>bool</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenInterval</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Regenable</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>NavigationLink</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -187,7 +187,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -204,49 +204,41 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>!CurrencyInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Coin_Gold</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gem_Diamond_Blue</t>
   </si>
   <si>
     <t>CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>!CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Coin_Gold</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gem_Diamond_Blue</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -383,55 +375,55 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,7 +707,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -742,7 +734,7 @@
         <v>22</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -780,7 +772,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -816,20 +808,20 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -1025,7 +1017,7 @@
       <c r="F21" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -33,7 +33,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -49,71 +49,71 @@
   </si>
   <si>
     <t>GoldDungeonTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ExpDungeonTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RaidTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>투기장 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>PVPTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>레이드 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenAmount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenMax</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>레이드 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>경험치 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>골드 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>투기장 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -141,7 +141,7 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -158,19 +158,19 @@
       </rPr>
       <t>bool</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenInterval</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Regenable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NavigationLink</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -187,7 +187,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -204,19 +204,19 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Coin_Gold</t>
@@ -226,19 +226,27 @@
   </si>
   <si>
     <t>CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -375,55 +383,55 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,7 +723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="4" bestFit="1" customWidth="1"/>
@@ -729,7 +737,7 @@
     <col min="10" max="10" width="14.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>22</v>
       </c>
@@ -741,7 +749,7 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B2" s="5" t="s">
         <v>1</v>
       </c>
@@ -770,7 +778,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
         <v>30</v>
       </c>
@@ -799,7 +807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
         <v>29</v>
       </c>
@@ -812,7 +820,7 @@
       </c>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
         <v>31</v>
       </c>
@@ -825,7 +833,7 @@
       </c>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
         <v>5</v>
@@ -850,7 +858,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
       <c r="B7" s="1" t="s">
         <v>6</v>
@@ -875,7 +883,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
       <c r="B8" s="1" t="s">
         <v>7</v>
@@ -900,7 +908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
       <c r="B9" s="9" t="s">
         <v>11</v>
@@ -925,56 +933,52 @@
         <v>5</v>
       </c>
       <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
       <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
       <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
       <c r="B13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="8"/>
       <c r="B14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="8"/>
       <c r="B15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="8"/>
       <c r="B16" s="1"/>
       <c r="D16" s="1"/>
@@ -1017,7 +1021,7 @@
       <c r="F21" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -33,7 +33,7 @@
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -49,71 +49,71 @@
   </si>
   <si>
     <t>GoldDungeonTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>ExpDungeonTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RaidTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>투기장 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>PVPTicket</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드던전 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경험치 던전 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>레이드 티켓</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenAmount</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenMax</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>레이드 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>경험치 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>골드 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>투기장 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -141,7 +141,7 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -158,19 +158,19 @@
       </rPr>
       <t>bool</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>RegenInterval</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Regenable</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>NavigationLink</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -187,7 +187,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -204,49 +204,41 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dia</t>
+    <phoneticPr fontId="7" type="noConversion"/>
+  </si>
+  <si>
+    <t>ItemIcon_Coin_Gold</t>
+  </si>
+  <si>
+    <t>ItemIcon_Gem_Diamond_Blue</t>
+  </si>
+  <si>
+    <t>CurrencyInfo</t>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dia</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>ItemIcon_Coin_Gold</t>
-  </si>
-  <si>
-    <t>ItemIcon_Gem_Diamond_Blue</t>
-  </si>
-  <si>
-    <t>CurrencyInfo</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <phoneticPr fontId="7" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -383,55 +375,55 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -715,7 +707,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -742,7 +734,7 @@
         <v>22</v>
       </c>
       <c r="B1" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -780,7 +772,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -816,20 +808,20 @@
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F5" s="1"/>
     </row>
@@ -1021,7 +1013,7 @@
       <c r="F21" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="8" type="noConversion"/>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -30,10 +30,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!ID</t>
@@ -48,72 +48,24 @@
     <t>!string</t>
   </si>
   <si>
-    <t>GoldDungeonTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>ExpDungeonTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>RaidTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
     <t>골드</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>다이아</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>투기장 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>PVPTicket</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드던전 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 던전 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이드 티켓</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenAmount</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!int</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenMax</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>레이드 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>경험치 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>골드 획득 던전 입장권(30분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>투기장 입장권(60분마다 1 획득)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -141,7 +93,7 @@
       </rPr>
       <t>Table</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -158,19 +110,19 @@
       </rPr>
       <t>bool</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RegenInterval</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Regenable</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NavigationLink</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -187,7 +139,7 @@
       </rPr>
       <t>con</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -204,15 +156,15 @@
       </rPr>
       <t>string</t>
     </r>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Gold</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Dia</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ItemIcon_Coin_Gold</t>
@@ -222,23 +174,39 @@
   </si>
   <si>
     <t>CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>!CurrencyInfo</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ruby</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>루비</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -375,55 +343,52 @@
   </borders>
   <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="3" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -707,7 +672,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -715,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="4" bestFit="1" customWidth="1"/>
@@ -730,11 +695,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="B1" s="15" t="s">
-        <v>33</v>
+      <c r="A1" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>21</v>
       </c>
       <c r="C1" s="3"/>
       <c r="D1" s="3"/>
@@ -751,28 +716,28 @@
       <c r="D2" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="14" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="G2" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H2" s="10" t="s">
+      <c r="E2" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="I2" s="10" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="13" t="s">
-        <v>26</v>
+      <c r="F2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="9" t="s">
+        <v>9</v>
+      </c>
+      <c r="J2" s="12" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B3" s="6" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>4</v>
@@ -780,174 +745,108 @@
       <c r="D3" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="G3" s="10" t="s">
+      <c r="E3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="H3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3" s="10" t="s">
+      <c r="F3" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="J3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="F4" s="1"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="1" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="1"/>
+        <v>24</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="8"/>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
-      </c>
-      <c r="D6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1800</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>10</v>
-      </c>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="8"/>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1800</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>10</v>
-      </c>
+      <c r="B7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="8"/>
-      <c r="B8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" t="s">
-        <v>14</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>18</v>
-      </c>
+      <c r="B8" s="1"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="1"/>
-      <c r="F8" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>3600</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>5</v>
-      </c>
+      <c r="F8" s="1"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="8"/>
-      <c r="B9" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" t="s">
-        <v>10</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="B9" s="1"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="1"/>
-      <c r="F9" s="1" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>3600</v>
-      </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>5</v>
-      </c>
-      <c r="J9" s="1"/>
+      <c r="F9" s="1"/>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
       <c r="B10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="8"/>
       <c r="B11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="8"/>
       <c r="B12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="8"/>
@@ -977,43 +876,8 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="8"/>
-      <c r="B17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="8"/>
-      <c r="B18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="8"/>
-      <c r="B19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="8"/>
-      <c r="B20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="8"/>
-      <c r="B21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-    </row>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Shared/XLS/Currency.xlsx
+++ b/Shared/XLS/Currency.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>!EnumTable</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -64,11 +64,35 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Gold</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Dia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Ruby</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>Currency</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Gold</t>
+    <t>일반적인 재화이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>유료 재화이다.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>부분유료 재화이다.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -482,7 +506,7 @@
     <col min="1" max="1" width="11.625" style="3" customWidth="1"/>
     <col min="2" max="2" width="15.875" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="28.375" style="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5" style="5" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.25" style="5" bestFit="1" customWidth="1"/>
@@ -497,7 +521,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C1" s="8"/>
       <c r="D1" s="8"/>
@@ -538,12 +562,17 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B4" s="7" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="7"/>
+      <c r="D4" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>13</v>
+      </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
       <c r="H4" s="7"/>
@@ -557,7 +586,12 @@
       <c r="C5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="7"/>
+      <c r="D5" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>14</v>
+      </c>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
@@ -571,7 +605,12 @@
       <c r="C6" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="7"/>
+      <c r="D6" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
